--- a/backend/data/raw/PRECIOS_PRODUCTOS_PAPELERIA.xlsx
+++ b/backend/data/raw/PRECIOS_PRODUCTOS_PAPELERIA.xlsx
@@ -511,7 +511,9 @@
       <c r="E2" s="5" t="n">
         <v>0.9396551724137931</v>
       </c>
-      <c r="F2" s="7" t="n"/>
+      <c r="F2" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Campos sin dato quedaron en blanco.</t>
@@ -536,6 +538,9 @@
       <c r="E3" s="5" t="n">
         <v>2.846153846153846</v>
       </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -849,6 +854,9 @@
       </c>
       <c r="E19" s="5" t="n">
         <v>0.4040999719180006</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2081,6 +2089,9 @@
       </c>
       <c r="E84" s="5" t="n">
         <v>4</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="85">
